--- a/client_data/client_5141/leads.xlsx
+++ b/client_data/client_5141/leads.xlsx
@@ -531,29 +531,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Restaurant in Una</t>
+          <t>Beauty Salon in Una</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Shri Guru Nanak Vaishno Dhaba</t>
+          <t>Hair Shakkers Una</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Chandigarh-Chintapurni-Dharamshala Rd, Ram Nagar, Una, Himachal Pradesh 174303, India</t>
+          <t>First floor opposite old bus stand, Nangal Rd, opposite maya hotel, Ram Nagar, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>063950 80017</t>
+          <t>086288 95100</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1489</v>
+        <v>2331</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -572,29 +572,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Restaurant in Una</t>
+          <t>Beauty Salon in Una</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>New Shri Guru Nanak Vaishno Dhaba</t>
+          <t>Gori Gius Makeup Studio</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2B-1/1005, Una - Amb Rd, opposite bachat bhawan . 174303, Ram Nagar, Prem Nagar, Una, Himachal Pradesh 174303, India</t>
+          <t>Ray'z Arcade, Rakkar, Shukrana resort, Nothern Railway Line, Chandigarh, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>098160 03058</t>
+          <t>083528 06757</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1293</v>
+        <v>665</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -613,29 +613,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Restaurant in Una</t>
+          <t>Hotel in Una</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Dr. Deo’z pizza &amp; Cafe Una</t>
+          <t>Hotel Natraj Palace</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Professor Colony, Una, Himachal Pradesh 174303, India</t>
+          <t>Natraj guest house, opp. D.C colony, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>099141 96062</t>
+          <t>097363 74450</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1018</v>
+        <v>630</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -654,29 +654,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Restaurant in Una</t>
+          <t>Hotel in Una</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Yankees Cafe and Restaurant</t>
+          <t>Hotel Tara</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SH 25, Behdala, Himachal Pradesh 174306, India</t>
+          <t>Vill. &amp; P.O. - Behdala, Nangal Road, NH 503, Una, Himachal Pradesh 174306, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>098051 15834</t>
+          <t>098167 64281</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>487</v>
+        <v>320</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -695,29 +695,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Restaurant in Una</t>
+          <t>Wedding Venue in Una</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Sambar</t>
+          <t>Royal Castle</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nangal Rd, opposite PNB Bank, near New ISBT, Ram Nagar, Una, Himachal Pradesh 174303, India</t>
+          <t>At, Old Hoshiarpur Rd, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>074034 20008</t>
+          <t>082194 21268</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -736,29 +736,29 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Fitness Center in Una</t>
+          <t>Beauty Salon in Una</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Diamond Gym Una</t>
+          <t>Styleo Unisex Salon and Makeup Studio</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nangal Rd, near Parth hotel, Professor Colony, Una, Himachal Pradesh 174303, India</t>
+          <t>Raizada Complex, Nangal Rd, below Diamond Gym, Professor Colony, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>080914 76805</t>
+          <t>070182 22628</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -777,29 +777,29 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Restaurant in Una</t>
+          <t>Hotel in Una</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>South Indian Kamachi Dosa</t>
+          <t>Krishna Hansraj Hotel</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>near Indira Ground, Professor Colony, Una, Himachal Pradesh 174303, India</t>
+          <t>Old Hoshiarpur Rd, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>090966 32992</t>
+          <t>075596 01777</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>169</v>
+        <v>271</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -818,29 +818,29 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Restaurant in Una</t>
+          <t>Beauty Salon in Una</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Delicious Bite Una</t>
+          <t>Plooksc a professional unisex salon</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Indira Stadium, near Government College, Professor Colony, Una, Himachal Pradesh 174303, India</t>
+          <t>Rampur road, near indian petrol pump, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>078009 78001</t>
+          <t>070185 01099</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -859,29 +859,29 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Fitness Center in Una</t>
+          <t>Wedding Venue in Una</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>B One Wellness The Premium Fitness Club</t>
+          <t>Sulaj Farms</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3rd Floor, The Kangans Building, Amb, Una - Hamirpur Rd, Friends Colony, Una, Himachal Pradesh 174303, India</t>
+          <t>Una Hamirpr Rd samoor kalan, G78Q+QJ5, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>070183 29560</t>
+          <t>094180 26663</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -900,29 +900,29 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Fitness Center in Una</t>
+          <t>Beauty Salon in Una</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sports central gym una</t>
+          <t>Hair Force Unisex Studio Una</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Una - Hamirpur Rd, near Suvidha Hotel, Una, Himachal Pradesh 174303, India</t>
+          <t>New Una estate, Near, Rakkar Bridge, Rakkar Colony, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>094183 50317</t>
+          <t>075298 96740</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -941,29 +941,29 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Restaurant in Una</t>
+          <t>Beauty Salon in Una</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>The Taste Temple</t>
+          <t>Hair Raiserz Luxe Una</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>above ISBT, Una, Himachal Pradesh 174303, India</t>
+          <t>Navjot Tower, Nangal Rd, near Realince Digital store, Professor Colony, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>098055 08890</t>
+          <t>082195 69156</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -982,29 +982,29 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Restaurant in Una</t>
+          <t>Wedding Venue in Una</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Arc Foods by Checkervartys</t>
+          <t>KRISHNA MARRIAGE PALACE</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2nd Floor, Arvind marg, New Market, opposite Ranjindra book store, Una, Himachal Pradesh 174303, India</t>
+          <t>Takka Rd, near RAILWAY BRIDGE, Dangehra, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>070185 26744</t>
+          <t>098050 72340</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -1023,29 +1023,29 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Restaurant in Una</t>
+          <t>Wedding Venue in Una</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Sambar House Una</t>
+          <t>Vijay decorator &amp; tent caterers events una Himachal</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CD Complex, College Road, Professor Colony, Una, Himachal Pradesh 174303, India</t>
+          <t>post office, Rampur, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>098052 79763</t>
+          <t>088946 53207</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -1064,29 +1064,29 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Real Estate Agency in Una</t>
+          <t>Beauty Salon in Una</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>The Designers Rajanil</t>
+          <t>Bandana's Royal Salon</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Amb Road, near Rotary Chowk, Una, Himachal Pradesh 174303, India</t>
+          <t>Ist Floor, Sangra Complex, near Traffic Chowk, Ram Nagar, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>094180 15316</t>
+          <t>094590 06006</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -1105,29 +1105,29 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Fitness Center in Una</t>
+          <t>Hotel in Una</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Fitness Point Gym</t>
+          <t>matangi hotel una</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Indira stadium, Nothern Railway Line, above Reliance smart bazaar, Professor Colony, Chandigarh, Una, Himachal Pradesh 174303, India</t>
+          <t>delwada road, nr. gayetri school, diu, Una, Gujarat 362510, India</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>086298 03939</t>
+          <t>072029 12111</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -1146,29 +1146,29 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Restaurant in Una</t>
+          <t>Hotel in Una</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D'GURU'S KITCHEN, SAFFRON UNIT-II</t>
+          <t>Hotel Moon</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>opposite DC Office, Una, Himachal Pradesh 174303, India</t>
+          <t>opposite old bus stand, Ram Nagar, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>082195 51236</t>
+          <t>082197 49938</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1187,29 +1187,29 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Fitness Center in Una</t>
+          <t>Beauty Salon in Una</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Tiger Gym Una</t>
+          <t>The GG Studio &amp; Academy</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Old Hoshiarpur Rd, near Royal Castle, Una, Himachal Pradesh 174303, India</t>
+          <t>SL Complex, Hamirpur road, near Axis bank, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>078075 18013</t>
+          <t>098821 21827</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1228,29 +1228,29 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Restaurant in Una</t>
+          <t>Beauty Salon in Una</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Shiv Shakti Cafe &amp; Dhaba</t>
+          <t>Hair Matters Beauty Salon</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>near by hill view colony, Jhalera, Una, Himachal Pradesh 174303, India</t>
+          <t>Una - Hamirpur Rd, near Civil Hospital, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>078762 77812</t>
+          <t>097792 51277</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1269,29 +1269,29 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Fitness Center in Una</t>
+          <t>Beauty Salon in Una</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ACMEYOGA</t>
+          <t>K Shine</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nangal Rd, Una, Himachal Pradesh 174303, India</t>
+          <t>Shop No. 10-11, Himachal Shopping Complex, Nangal Rd, near Govt. College, Professor Colony, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>091159 51905</t>
+          <t>098821 20860</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>148</v>
+        <v>333</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/acmeyoga_una?igsh=cHV6YXcydXM2MzV3</t>
+          <t>https://www.facebook.com/kshineuna/</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1314,29 +1314,29 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Real Estate Agency in Una</t>
+          <t>photography studios in Una</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>GALAXY ART PHOTOGRAPHY UNA HIMACHAL PRADESH</t>
+          <t>Sanchit dogra photography</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>174303 2B-1/1005, Una-Amb Road, shop no 2, Gurusar mohalla 1 floor, Road, opposite Khas khulfi, Ram Nagar, Takka, Una, Himachal Pradesh 174303, India</t>
+          <t>ward no 4, near fisheries department, Vikas Nagar, Professor Colony, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>070180 07186</t>
+          <t>097791 67872</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/galaxy_art_photography_una/</t>
+          <t>https://www.instagram.com/sanchitdogra_photography?igsh=MWt4OGlqN3R0aWczOQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>

--- a/client_data/client_5141/leads.xlsx
+++ b/client_data/client_5141/leads.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$L$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -469,6 +469,7 @@
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -519,10 +520,15 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>E-commerce Platform</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Weak Points</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PageSpeed Score (mobile)</t>
         </is>
@@ -531,29 +537,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Beauty Salon in Una</t>
+          <t>Restaurant in Nangal</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Hair Shakkers Una</t>
+          <t>Hot Billions</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>First floor opposite old bus stand, Nangal Rd, opposite maya hotel, Ram Nagar, Una, Himachal Pradesh 174303, India</t>
+          <t>Sector 2, Naya Nangal, Punjab 140126, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>086288 95100</t>
+          <t>096463 00736</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2331</v>
+        <v>1842</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -568,33 +574,34 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Beauty Salon in Una</t>
+          <t>Restaurant in Nangal</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Gori Gius Makeup Studio</t>
+          <t>Chaudhary Bishan Dass Ji Da Dhabba</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Ray'z Arcade, Rakkar, Shukrana resort, Nothern Railway Line, Chandigarh, Una, Himachal Pradesh 174303, India</t>
+          <t>222-258, Railway Road, Nangal, Hambewal, Punjab 140124, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>083528 06757</t>
+          <t>098782 64775</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>665</v>
+        <v>988</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -609,33 +616,34 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Hotel in Una</t>
+          <t>Restaurant in Nangal</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Hotel Natraj Palace</t>
+          <t>Da Headquarter Restaurant &amp; Cafe</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Natraj guest house, opp. D.C colony, Una, Himachal Pradesh 174303, India</t>
+          <t>Da Headquarter, Anandpur Road, Brahmpur, Nangal, Punjab 140125, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>097363 74450</t>
+          <t>098157 52413</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>630</v>
+        <v>517</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -650,33 +658,34 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Hotel in Una</t>
+          <t>Wedding Venue in Una</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Hotel Tara</t>
+          <t>Inder Palace</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Vill. &amp; P.O. - Behdala, Nangal Road, NH 503, Una, Himachal Pradesh 174306, India</t>
+          <t>985G+2FV, Nangal Rd, Santokhgarh, Himachal Pradesh 174301, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>098167 64281</t>
+          <t>098821 85007</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>320</v>
+        <v>425</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -691,33 +700,34 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Wedding Venue in Una</t>
+          <t>Restaurant in Nangal</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Royal Castle</t>
+          <t>Divine Sip</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>At, Old Hoshiarpur Rd, Una, Himachal Pradesh 174303, India</t>
+          <t>gurdara road, near taxi stand, Nangal Town Ship, Divine sip, purana, Nangal, Punjab 140124, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>082194 21268</t>
+          <t>085590 12047</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -732,33 +742,34 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Beauty Salon in Una</t>
+          <t>Restaurant in Nangal</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Styleo Unisex Salon and Makeup Studio</t>
+          <t>Daawat Restaurant &amp; Dhaba</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Raizada Complex, Nangal Rd, below Diamond Gym, Professor Colony, Una, Himachal Pradesh 174303, India</t>
+          <t>Nangal, Road, Kalsera, Punjab 140126, India</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>070182 22628</t>
+          <t>098723 95532</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -773,33 +784,34 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Hotel in Una</t>
+          <t>Restaurant in Nangal</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Krishna Hansraj Hotel</t>
+          <t>Punjab Café</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Old Hoshiarpur Rd, Una, Himachal Pradesh 174303, India</t>
+          <t>MP Di Kothi, Meda Majra, Nangal, Punjab 140125, India</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>075596 01777</t>
+          <t>070094 91836</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -814,33 +826,34 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Beauty Salon in Una</t>
+          <t>Restaurant in Nangal</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Plooksc a professional unisex salon</t>
+          <t>Swami South Indian</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Rampur road, near indian petrol pump, Una, Himachal Pradesh 174303, India</t>
+          <t>Shop no 14, main market, DD block, Nangal, Punjab 140124, India</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>070185 01099</t>
+          <t>083604 13357</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -855,33 +868,34 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Wedding Venue in Una</t>
+          <t>Restaurant in Nangal</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sulaj Farms</t>
+          <t>Kaushalya Sweets</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Una Hamirpr Rd samoor kalan, G78Q+QJ5, Una, Himachal Pradesh 174303, India</t>
+          <t>Railway Road, near Bata showroom, Nangal, Dohkli, Punjab 140124, India</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>094180 26663</t>
+          <t>099158 11123</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>181</v>
+        <v>137</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -896,33 +910,34 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Beauty Salon in Una</t>
+          <t>Fitness Center in Nangal</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Hair Force Unisex Studio Una</t>
+          <t>MOD FITNESS</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>New Una estate, Near, Rakkar Bridge, Rakkar Colony, Una, Himachal Pradesh 174303, India</t>
+          <t>Modern Complex, Khwaja Mandir Road, RAJ NAGAR, Nangal, Hambewal, Punjab 140124, India</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>075298 96740</t>
+          <t>088725 18585</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -937,33 +952,34 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Beauty Salon in Una</t>
+          <t>Restaurant in Nangal</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Hair Raiserz Luxe Una</t>
+          <t>Ninu Dhaba</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Navjot Tower, Nangal Rd, near Realince Digital store, Professor Colony, Una, Himachal Pradesh 174303, India</t>
+          <t>Nangal Town Ship, Nangal, Punjab 140124, India</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>082195 69156</t>
+          <t>085285 99543</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -978,33 +994,34 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Wedding Venue in Una</t>
+          <t>Restaurant in Nangal</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>KRISHNA MARRIAGE PALACE</t>
+          <t>SHARMA HOTEL</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Takka Rd, near RAILWAY BRIDGE, Dangehra, Una, Himachal Pradesh 174303, India</t>
+          <t>17 Main Market, Nangal, Punjab 140124, India</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>098050 72340</t>
+          <t>079736 09695</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -1019,33 +1036,34 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Wedding Venue in Una</t>
+          <t>Restaurant in Nangal</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Vijay decorator &amp; tent caterers events una Himachal</t>
+          <t>Sindhwani Dhaba</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>post office, Rampur, Una, Himachal Pradesh 174303, India</t>
+          <t>99HC+5H5, Adda Market, Nangal, Hambewal, Punjab 140124, India</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>088946 53207</t>
+          <t>098157 52413</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -1060,33 +1078,34 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Beauty Salon in Una</t>
+          <t>Restaurant in Nangal</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Bandana's Royal Salon</t>
+          <t>Babbu Da Dhaba</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Ist Floor, Sangra Complex, near Traffic Chowk, Ram Nagar, Una, Himachal Pradesh 174303, India</t>
+          <t>Shop no 6, Adda Market, Nangal, Hambewal, Punjab 140124, India</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>094590 06006</t>
+          <t>076964 16019</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -1101,197 +1120,218 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Hotel in Una</t>
+          <t>photography studios in Una</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>matangi hotel una</t>
+          <t>Rana Studio Photography</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>delwada road, nr. gayetri school, diu, Una, Gujarat 362510, India</t>
+          <t>NH503, Ward Number 6, Ward Number 4, Basdehra, Mehatpur, Himachal Pradesh 174315, India</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>072029 12111</t>
+          <t>093185 80204</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>259</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rana_studio_photography_/</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Hotel in Una</t>
+          <t>Fitness Center in Nangal</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Hotel Moon</t>
+          <t>THE FALCON GYM</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>opposite old bus stand, Ram Nagar, Una, Himachal Pradesh 174303, India</t>
+          <t>Shivalik Avenue, phase 1A, Naya Nangal, Ajouli, Punjab 140126, India</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>082197 49938</t>
+          <t>098774 49913</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>224</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the_falcon_gym_022?igshid=ODA1NTc5OTg5Nw==</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Beauty Salon in Una</t>
+          <t>Fitness Center in Nangal</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>The GG Studio &amp; Academy</t>
+          <t>B one gym (fitnation)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SL Complex, Hamirpur road, near Axis bank, Una, Himachal Pradesh 174303, India</t>
+          <t>near Axis Bank, Kalsera, Nangal, Kalsera, Punjab 140126, India</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>098821 21827</t>
+          <t>076960 64519</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>184</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/b_one_gym_?igsh=MTAyanRmOXY4a2kzdg==</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Beauty Salon in Una</t>
+          <t>fitness centers in Una</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Hair Matters Beauty Salon</t>
+          <t>PhysioZone4U</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Una - Hamirpur Rd, near Civil Hospital, Una, Himachal Pradesh 174303, India</t>
+          <t>166/6, Hamipur Road, near Regional hospital, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>097792 51277</t>
+          <t>098889 70270</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>166</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/physiozone4u_move_to_heal?r=nametag,</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Beauty Salon in Una</t>
+          <t>photography studios in Una</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>K Shine</t>
+          <t>Kumar Studio Una</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Shop No. 10-11, Himachal Shopping Complex, Nangal Rd, near Govt. College, Professor Colony, Una, Himachal Pradesh 174303, India</t>
+          <t>Main Bazaar Rd, near govt girl school, Ram Nagar, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>098821 20860</t>
+          <t>078766 50258</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>333</v>
+        <v>105</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
@@ -1305,11 +1345,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kshineuna/</t>
+          <t>https://www.instagram.com/kumarstudiouna?igsh=MXJubDRwdnFleWJ0eg==</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1319,24 +1360,24 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Sanchit dogra photography</t>
+          <t>Dogra Photography Studio Una</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ward no 4, near fisheries department, Vikas Nagar, Professor Colony, Una, Himachal Pradesh 174303, India</t>
+          <t>WARD NO 04, Vikas Nagar, Professor Colony, Una, Himachal Pradesh 174303, India</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>097791 67872</t>
+          <t>082199 03479</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>154</v>
+        <v>57</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -1350,14 +1391,15 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sanchitdogra_photography?igsh=MWt4OGlqN3R0aWczOQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/dographotographyuna?igsh=MXA5YTVyZGR0OTdwbQ==</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K21"/>
+  <autoFilter ref="A1:L21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>